--- a/output/pdf_financials_xlsx/ALAB.P.xlsx
+++ b/output/pdf_financials_xlsx/ALAB.P.xlsx
@@ -853,16 +853,16 @@
         <v>-0.13394</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.140474</v>
+        <v>-0.140474</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.170932</v>
+        <v>-0.170932</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.027921</v>
+        <v>-0.027921</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.023156</v>
+        <v>-0.023156</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -995,16 +995,16 @@
         <v>-0.13394</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.140474</v>
+        <v>-0.140474</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.170932</v>
+        <v>-0.170932</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.027921</v>
+        <v>-0.027921</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.023156</v>
+        <v>-0.023156</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
         <v>-0.13394</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.140474</v>
+        <v>-0.140474</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.170932</v>
+        <v>-0.170932</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.027921</v>
+        <v>-0.027921</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.023156</v>
+        <v>-0.023156</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>1.67425</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2.065794</v>
+        <v>-2.065794</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2.059422</v>
+        <v>-2.059422</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1.994357</v>
+        <v>-1.994357</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-2.105091</v>
+        <v>2.105091</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1203,16 +1203,16 @@
         <v>-0.13394</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.140474</v>
+        <v>-0.140474</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.170932</v>
+        <v>-0.170932</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.027921</v>
+        <v>-0.027921</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.023156</v>
+        <v>-0.023156</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1261,16 +1261,16 @@
         <v>-0.13394</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.140474</v>
+        <v>-0.140474</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.170932</v>
+        <v>-0.170932</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.027921</v>
+        <v>-0.027921</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.023156</v>
+        <v>-0.023156</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1333,16 +1333,16 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         <v>-0.13394</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.140474</v>
+        <v>-0.140474</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.170932</v>
+        <v>-0.170932</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.027921</v>
@@ -8634,10 +8634,10 @@
         </is>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.027921</v>
+        <v>-0.027921</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0.023156</v>
+        <v>-0.023156</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -8832,10 +8832,10 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.140474</v>
+        <v>-0.140474</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.170932</v>
+        <v>-0.170932</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ALAB.P.xlsx
+++ b/output/pdf_financials_xlsx/ALAB.P.xlsx
@@ -683,13 +683,13 @@
         <v>0.03149</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.111083</v>
+        <v>0.140474</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.134432</v>
+        <v>0.170932</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.006284</v>
+        <v>0.027921</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.008064999999999999</v>
@@ -711,13 +711,13 @@
         <v>-0.03149</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.111083</v>
+        <v>-0.140474</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.134432</v>
+        <v>-0.170932</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.006284</v>
+        <v>-0.027921</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.008064999999999999</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.165141</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.165141</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.182543</v>
+        <v>0.017402</v>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -8023,10 +8023,10 @@
         <v>0.027921</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>-0.023156</v>
+        <v>0.023156</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.050426</v>
+        <v>0.050426</v>
       </c>
     </row>
     <row r="62">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">

--- a/output/pdf_financials_xlsx/ALAB.P.xlsx
+++ b/output/pdf_financials_xlsx/ALAB.P.xlsx
@@ -457,12 +457,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-12</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -1408,25 +1408,17 @@
       <c r="B34" s="3" t="n">
         <v>0.165141</v>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v>0.231779</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0.068048</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.027697</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.013439</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.000269</v>
@@ -1444,25 +1436,17 @@
       <c r="B35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -1480,25 +1464,17 @@
       <c r="B36" s="3" t="n">
         <v>0.165141</v>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v>0.231779</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.068048</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.027697</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0.013439</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.000269</v>
@@ -1516,25 +1492,17 @@
       <c r="B37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
@@ -1552,25 +1520,17 @@
       <c r="B38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0</v>
@@ -1588,25 +1548,17 @@
       <c r="B39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
@@ -1624,25 +1576,17 @@
       <c r="B40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
@@ -1660,25 +1604,17 @@
       <c r="B41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0</v>
@@ -1696,25 +1632,17 @@
       <c r="B42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0</v>
@@ -1732,25 +1660,17 @@
       <c r="B43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0</v>
@@ -1768,25 +1688,17 @@
       <c r="B44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>0</v>
@@ -1804,25 +1716,17 @@
       <c r="B45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0</v>
@@ -1840,25 +1744,17 @@
       <c r="B46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>0</v>
@@ -1876,25 +1772,17 @@
       <c r="B47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0</v>
@@ -1912,25 +1800,17 @@
       <c r="B48" s="3" t="n">
         <v>0.017402</v>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -1948,30 +1828,20 @@
       <c r="B49" s="3" t="n">
         <v>0.182543</v>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C49" s="3" t="n">
+        <v>0.231779</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.068048</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.027697</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>0.013439</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.000269</v>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
@@ -1988,25 +1858,17 @@
       <c r="B50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>0</v>
@@ -2024,25 +1886,17 @@
       <c r="B51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0</v>
@@ -2060,25 +1914,17 @@
       <c r="B52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>0</v>
@@ -2096,25 +1942,17 @@
       <c r="B53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0</v>
@@ -2132,25 +1970,17 @@
       <c r="B54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0</v>
@@ -2210,25 +2040,17 @@
       <c r="B56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0</v>
@@ -2246,25 +2068,17 @@
       <c r="B57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0</v>
@@ -2282,25 +2096,17 @@
       <c r="B58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0</v>
@@ -2318,25 +2124,17 @@
       <c r="B59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0</v>
@@ -2354,25 +2152,17 @@
       <c r="B60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0</v>
@@ -2390,25 +2180,17 @@
       <c r="B61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0</v>
@@ -2448,10 +2230,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
@@ -2506,25 +2286,17 @@
       <c r="B64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -2542,25 +2314,17 @@
       <c r="B65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0</v>
@@ -2578,25 +2342,17 @@
       <c r="B66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0</v>
@@ -2614,25 +2370,17 @@
       <c r="B67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -2650,25 +2398,17 @@
       <c r="B68" s="3" t="n">
         <v>0.016524</v>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C68" s="3" t="n">
+        <v>0.025043</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.035531</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.166112</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.154775</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.164761</v>
@@ -2686,25 +2426,17 @@
       <c r="B69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
@@ -2722,25 +2454,17 @@
       <c r="B70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0</v>
@@ -2758,25 +2482,17 @@
       <c r="B71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
@@ -2794,25 +2510,17 @@
       <c r="B72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G72" s="3" t="n">
         <v>0</v>
@@ -2830,25 +2538,17 @@
       <c r="B73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0</v>
@@ -2866,25 +2566,17 @@
       <c r="B74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
         <v>0</v>
@@ -2902,28 +2594,20 @@
       <c r="B75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.025</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0</v>
@@ -2955,15 +2639,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="3" t="n">
+        <v>0.179775</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0.189761</v>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
@@ -2980,25 +2660,17 @@
       <c r="B77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0</v>
@@ -3016,25 +2688,17 @@
       <c r="B78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0</v>
@@ -3052,25 +2716,17 @@
       <c r="B79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0</v>
@@ -3130,25 +2786,17 @@
       <c r="B81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0</v>
@@ -3166,25 +2814,17 @@
       <c r="B82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0</v>
@@ -3202,25 +2842,17 @@
       <c r="B83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
@@ -3238,25 +2870,17 @@
       <c r="B84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0</v>
@@ -3274,25 +2898,17 @@
       <c r="B85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>0</v>
@@ -3332,10 +2948,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
@@ -3390,25 +3004,17 @@
       <c r="B88" s="3" t="n">
         <v>0.185</v>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C88" s="3" t="n">
+        <v>0.306518</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.316129</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.316129</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.316129</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>0.316129</v>
@@ -3426,25 +3032,17 @@
       <c r="B89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0</v>
@@ -3462,25 +3060,17 @@
       <c r="B90" s="3" t="n">
         <v>-0.018981</v>
       </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C90" s="3" t="n">
+        <v>-0.152921</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>-0.326191</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-0.497123</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>-0.525044</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>-0.5482</v>
@@ -3498,25 +3088,17 @@
       <c r="B91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
@@ -3534,25 +3116,17 @@
       <c r="B92" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C92" s="3" t="n">
+        <v>0.053139</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0.042579</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.042579</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.042579</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0.042579</v>
@@ -3570,25 +3144,17 @@
       <c r="B93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
@@ -3606,25 +3172,17 @@
       <c r="B94" s="3" t="n">
         <v>0.166019</v>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C94" s="3" t="n">
+        <v>0.206736</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.032517</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.138415</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>-0.166336</v>
       </c>
       <c r="G94" s="3" t="n">
         <v>-0.189492</v>
@@ -3642,25 +3200,17 @@
       <c r="B95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
@@ -3678,25 +3228,17 @@
       <c r="B96" s="3" t="n">
         <v>0.166019</v>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C96" s="3" t="n">
+        <v>0.206736</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.032517</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.138415</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>-0.166336</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>-0.189492</v>
@@ -4833,7 +4375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4940,10 +4482,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="5" t="n">
+        <v>0.013439</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>0.000269</v>
@@ -5046,10 +4586,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="5" t="n">
+        <v>0.154775</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>0.164761</v>
@@ -5403,20 +4941,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G11" s="5" t="n">
+        <v>-0.326191</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.497123</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>-0.525044</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>-0.5482</v>
@@ -5544,41 +5076,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cash (Note 4) $</t>
+          <t>Current total</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.165141</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.182543</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.231779</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.068048</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.027697</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.013439</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0.000269</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -5599,12 +5121,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deferred share issuance costs</t>
+          <t>Promissory notes payable (Note 8)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" s="5" t="n">
-        <v>0.017402</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -5621,15 +5145,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -5645,46 +5165,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Shareholders' Equity (Deficiency)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Current total</t>
+          <t>Capital stock (Note 5)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0.182543</v>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G16" s="5" t="n">
+        <v>0.316129</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.316129</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0.316129</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0.316129</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -5700,46 +5214,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Shareholders' Equity (Deficiency)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities $</t>
+          <t>Contributed surplus</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>0.016524</v>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G17" s="5" t="n">
+        <v>0.042579</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.042579</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.042579</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.042579</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -5755,46 +5263,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shareholders' Equity</t>
+          <t>Shareholders' Equity (Deficiency)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Capital stock (Note 5)</t>
+          <t>Shareholders' Equity (Deficiency) total</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>0.185</v>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G18" s="5" t="n">
+        <v>0.032517</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-0.138415</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.166336</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>-0.189492</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -5810,36 +5312,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shareholders' Equity</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Retained earnings (deficit)</t>
+          <t>Cash and cash equivalents (Note 4) $</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.018981</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.165141</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.231779</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.068048</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.027697</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5865,36 +5361,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shareholders' Equity</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shareholders' Equity total</t>
+          <t>Accounts payable and accrued liabilities $</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.166019</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016524</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.025043</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.035531</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.166112</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5920,17 +5410,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shareholders' Equity</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nature of Operations (Note</t>
+          <t>Deferred share issuance costs</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.017402</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -5976,17 +5466,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Subsequent Events (Note</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Capital stock (Note 5)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.185</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.306518</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6017,29 +5509,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Net loss before tax</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Contributed surplus</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="5" t="n">
+        <v>0.053139</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6056,39 +5550,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J23" s="5" t="n">
-        <v>-0.023156</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>-0.045004</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adjustment for non-cash and other items</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Liabilities written off</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-0.018981</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.152921</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6110,40 +5608,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K24" s="5" t="n">
-        <v>-0.005422</v>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adjustment for working capital changes</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Decrease in accounts payable and accrued liabilities</t>
+          <t>Shareholders' Equity total</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.166019</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.206736</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6160,34 +5656,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="5" t="n">
-        <v>0.009986</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>-0.09389400000000001</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adjustment for working capital changes</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Increase in due to related parties</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash (Note 4) $</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.165141</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -6214,35 +5716,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="5" t="n">
-        <v>0.015764</v>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adjustment for working capital changes</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cash provided by (used in) operating activities</t>
+          <t>Retained earnings (deficit)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-0.018981</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -6264,38 +5766,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>-0.01317</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>-0.128556</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adjustment for working capital changes</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Nature of Operations (Note</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -6331,24 +5831,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Shareholders' Equity</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Proceeds from capital subscription</t>
+          <t>Subsequent Events (Note</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="5" t="n">
+        <v>1e-05</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -6375,8 +5873,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n">
-        <v>0.024985</v>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -6387,12 +5887,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Promissory notes payable</t>
+          <t>Net loss before tax</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -6421,13 +5921,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J30" s="5" t="n">
+        <v>-0.023156</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.128375</v>
+        <v>-0.045004</v>
       </c>
     </row>
     <row r="31">
@@ -6438,19 +5936,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Adjustment for non-cash and other items</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash provided by (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Liabilities written off</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -6482,7 +5976,7 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.15336</v>
+        <v>-0.005422</v>
       </c>
     </row>
     <row r="32">
@@ -6493,17 +5987,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Adjustment for working capital changes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Net change in cash and cash equivalents</t>
+          <t>Decrease in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6532,10 +6026,10 @@
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-0.01317</v>
+        <v>0.009986</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.024804</v>
+        <v>-0.09389400000000001</v>
       </c>
     </row>
     <row r="33">
@@ -6546,12 +6040,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Adjustment for working capital changes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at the beginning of the year</t>
+          <t>Increase in due to related parties</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -6580,11 +6074,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J33" s="5" t="n">
-        <v>0.013439</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.000269</v>
+        <v>0.015764</v>
       </c>
     </row>
     <row r="34">
@@ -6595,15 +6091,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Adjustment for working capital changes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at the end of the year</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Cash provided by (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -6630,10 +6130,10 @@
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0.000269</v>
+        <v>-0.01317</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.025073</v>
+        <v>-0.128556</v>
       </c>
     </row>
     <row r="35">
@@ -6644,17 +6144,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Adjustment for working capital changes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6677,11 +6177,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n">
-        <v>-0.027921</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>-0.023156</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -6697,41 +6201,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0.016524</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0.008519000000000001</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.007133</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>0.130581</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>-0.011337</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>0.009986</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from capital subscription</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0.024985</v>
       </c>
     </row>
     <row r="37">
@@ -6742,19 +6252,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash (used in) operating activities</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Promissory notes payable</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -6765,22 +6271,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n">
-        <v>-0.133341</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>-0.040351</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>-0.039258</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>-0.01317</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0.128375</v>
       </c>
     </row>
     <row r="38">
@@ -6791,15 +6303,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Promissory notes payable</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Cash provided by (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -6820,18 +6336,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n">
-        <v>0.025</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K38" s="5" t="n">
+        <v>0.15336</v>
       </c>
     </row>
     <row r="39">
@@ -6842,15 +6358,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cash provided in financing activities</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Net change in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -6871,18 +6391,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>-0.01317</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0.024804</v>
       </c>
     </row>
     <row r="40">
@@ -6893,19 +6411,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Cash and cash equivalents at the beginning of the year</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -6916,22 +6430,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>-0.127051</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>-0.040351</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>-0.014258</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.01317</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013439</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0.000269</v>
       </c>
     </row>
     <row r="41">
@@ -6942,19 +6460,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Cash and cash equivalents at the end of the year</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -6965,22 +6479,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>0.195099</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>0.068048</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>0.027697</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.013439</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000269</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0.025073</v>
       </c>
     </row>
     <row r="42">
@@ -6991,17 +6509,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -7025,10 +6543,10 @@
         </is>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.013439</v>
+        <v>-0.027921</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>0.000269</v>
+        <v>-0.023156</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -7044,42 +6562,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Exercise of options (note 4)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.016524</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.008519000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.00629</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007133</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.130581</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>-0.011337</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0.009986</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -7095,17 +6607,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Cash (used in) operating activities</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -7119,20 +6631,16 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.068048</v>
+        <v>-0.133341</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.027697</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.040351</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.039258</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>-0.01317</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -7148,24 +6656,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>-0.018981</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>-0.13394</v>
+          <t>Promissory notes payable</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7177,10 +6685,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -7201,26 +6707,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Cash provided in financing activities</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>0.042579</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7232,10 +6736,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -7256,40 +6758,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Items not affecting cash total</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>-0.018981</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>-0.091361</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.127051</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-0.040351</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>-0.014258</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-0.01317</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -7305,44 +6807,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Deferred share issuance costs</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>-0.017402</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0.017402</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.195099</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.068048</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0.027697</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0.013439</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -7358,24 +6856,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>-0.019859</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-0.06544</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7387,15 +6889,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="5" t="n">
+        <v>0.013439</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.000269</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -7416,24 +6914,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Issuance of capital stock (Note 5)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>IssuanceOfCapitalStock</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exercise of options (note 4)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.00629</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -7469,12 +6965,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7482,18 +6978,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>-0.067922</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.068048</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.027697</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -7519,24 +7013,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Financing Activity total</t>
+          <t>Net loss for the period $</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.185</v>
+        <v>-0.018981</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.132078</v>
+        <v>-0.13394</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -7572,24 +7066,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Net change in cash during the period</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0.165141</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.066638</v>
+        <v>0.042579</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -7625,26 +7121,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Items not affecting cash total</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>-0.018981</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.165141</v>
+        <v>-0.091361</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -7680,24 +7170,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financing Activity</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>Deferred share issuance costs</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.165141</v>
+        <v>-0.017402</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.231779</v>
+        <v>0.017402</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7738,7 +7228,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cash provided by/(used in) operating activities</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7749,10 +7239,8 @@
       <c r="E56" s="5" t="n">
         <v>-0.019859</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F56" s="5" t="n">
+        <v>-0.06544</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7793,7 +7281,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Issuance of capital stock</t>
+          <t>Issuance of capital stock (Note 5)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7804,10 +7292,8 @@
       <c r="E57" s="5" t="n">
         <v>0.185</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F57" s="5" t="n">
+        <v>0.2</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7838,22 +7324,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Share issuance costs</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7861,10 +7347,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F58" s="5" t="n">
+        <v>-0.067922</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7881,84 +7365,96 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J58" s="5" t="n">
-        <v>0.00575</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>0.017146</v>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Audit and accounting</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.014029</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>0.02229</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>0.010882</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>-0.009341</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>-0.0117</v>
+          <t>Financing Activity total</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.132078</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net change in cash during the period</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0.165141</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.03149</v>
+        <v>0.066638</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7975,32 +7471,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J60" s="5" t="n">
-        <v>0.008064999999999999</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0.02158</v>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -8008,53 +7508,61 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.140474</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>0.170932</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>0.027921</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>0.023156</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>0.050426</v>
+      <c r="F61" s="5" t="n">
+        <v>0.165141</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Liabilities written off (Note 10)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0.165141</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0.231779</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -8076,31 +7584,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K62" s="5" t="n">
-        <v>0.005422</v>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Loss before tax</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash provided by/(used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>-0.019859</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8122,38 +7634,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J63" s="5" t="n">
-        <v>-0.023156</v>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>-0.045004</v>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Financing Activity</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Issuance of capital stock</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8194,15 +7708,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Loss, net of taxes</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -8229,10 +7747,10 @@
         </is>
       </c>
       <c r="J65" s="5" t="n">
-        <v>-0.023156</v>
+        <v>0.00575</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.045004</v>
+        <v>0.017146</v>
       </c>
     </row>
     <row r="66">
@@ -8243,12 +7761,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Audit and accounting</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -8262,30 +7780,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G66" s="5" t="n">
+        <v>0.014029</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0.02229</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.010882</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>-0.009341</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>-0.0117</v>
       </c>
     </row>
     <row r="67">
@@ -8296,24 +7804,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Total Comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="5" t="n">
+        <v>0.03149</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8331,10 +7841,10 @@
         </is>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.023156</v>
+        <v>0.008064999999999999</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.045004</v>
+        <v>0.02158</v>
       </c>
     </row>
     <row r="68">
@@ -8345,17 +7855,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8368,26 +7878,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" s="5" t="n">
+        <v>0.140474</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.170932</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.027921</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-1.1e-08</v>
+        <v>0.023156</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-2.2e-08</v>
+        <v>0.050426</v>
       </c>
     </row>
     <row r="69">
@@ -8398,12 +7902,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Weighted average number of shares</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Weighted average number of shares total</t>
+          <t>Liabilities written off (Note 10)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -8432,11 +7936,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J69" s="5" t="n">
-        <v>2.0629</v>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>2.0629</v>
+        <v>0.005422</v>
       </c>
     </row>
     <row r="70">
@@ -8447,19 +7953,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Loss before tax</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -8480,16 +7982,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n">
-        <v>0.006284</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="5" t="n">
-        <v>0.00575</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.023156</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>-0.045004</v>
       </c>
     </row>
     <row r="71">
@@ -8500,15 +8002,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Operating</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Income tax expense</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -8519,17 +8025,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n">
-        <v>0.015362</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>0.01421</v>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>0.010564</v>
-      </c>
-      <c r="J71" s="5" t="n">
-        <v>0.008064999999999999</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -8545,19 +8059,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Loss, net of taxes</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -8578,18 +8088,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n">
-        <v>0.000191</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>-0.023156</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>-0.045004</v>
       </c>
     </row>
     <row r="73">
@@ -8600,19 +8108,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -8633,11 +8137,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n">
-        <v>-0.027921</v>
-      </c>
-      <c r="J73" s="5" t="n">
-        <v>-0.023156</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -8653,19 +8161,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Total Comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -8686,16 +8190,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n">
-        <v>1.4e-08</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>1.1e-08</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.023156</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>-0.045004</v>
       </c>
     </row>
     <row r="75">
@@ -8706,17 +8210,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Weighted average number of shares</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (Note 5)</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8729,22 +8233,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G75" s="5" t="n">
-        <v>2.052417</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>2.0629</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>2.0629</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="5" t="n">
-        <v>2.0629</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.1e-08</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>-2.2e-08</v>
       </c>
     </row>
     <row r="76">
@@ -8755,19 +8263,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Legal $</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Weighted average number of shares total</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -8778,26 +8282,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" s="5" t="n">
-        <v>0.111083</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>0.134432</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J76" s="5" t="n">
+        <v>2.0629</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>2.0629</v>
       </c>
     </row>
     <row r="77">
@@ -8808,17 +8312,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8831,21 +8335,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G77" s="5" t="n">
-        <v>-0.140474</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>-0.170932</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0.006284</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>0.00575</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -8861,19 +8365,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Basic and dilute loss per share</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Operating</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -8885,20 +8385,16 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>6.8e-08</v>
+        <v>0.015362</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>8.3e-08</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01421</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0.010564</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>0.008064999999999999</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -8919,15 +8415,23 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Legal costs $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>0.018981</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>0.045432</v>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -8939,10 +8443,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="5" t="n">
+        <v>0.000191</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -8963,22 +8465,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss and comprehensive loss for the</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Audit fees</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F80" s="5" t="n">
-        <v>0.014439</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8990,15 +8498,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="5" t="n">
+        <v>-0.027921</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>-0.023156</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -9014,22 +8518,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss and comprehensive loss for the</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>0.042579</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -9041,15 +8551,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="5" t="n">
+        <v>1.4e-08</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>1.1e-08</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -9065,44 +8571,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Weighted average number of shares outstanding (Note 5)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>0.018981</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>0.13394</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>2.052417</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>2.0629</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>2.0629</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>2.0629</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -9123,29 +8625,29 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Legal $</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>-0.018981</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>-0.13394</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.111083</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.134432</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -9171,17 +8673,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Loss per Share</t>
+          <t>Net loss and comprehensive loss for the</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Basic and diluted per share $</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9189,18 +8691,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>-8e-08</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>-0.140474</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>-0.170932</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -9226,17 +8726,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Loss per Share</t>
+          <t>Net loss and comprehensive loss for the</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Basic and dilute loss per share</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9244,18 +8744,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>1.605479</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>6.8e-08</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>8.3e-08</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -9286,43 +8784,410 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>Legal costs $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>0.018981</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0.045432</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Audit fees</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.014439</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Stock based compensation</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.042579</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.018981</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.13394</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>-0.018981</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-0.13394</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Loss per Share</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Basic and diluted per share $</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Loss per Share</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>1.605479</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>Net loss and comprehensive loss, for the period $</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E86" s="5" t="n">
+      <c r="E93" s="5" t="n">
         <v>-0.018981</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
